--- a/tools/importer/reports/import-product-detail-page.report.xlsx
+++ b/tools/importer/reports/import-product-detail-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="265">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,66 @@
     <t>url</t>
   </si>
   <si>
+    <t>en.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","hero-video","columns","carousel","cards-icon","columns-cta","cards-news","columns-banner"]</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:56:22.705Z</t>
+  </si>
+  <si>
+    <t>Zimmer Biomet: Innovations in Orthopedic Care</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en</t>
+  </si>
+  <si>
+    <t>en/education-and-resources.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>en/education-and-resources</t>
+  </si>
+  <si>
+    <t>generic</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:05:18.431Z</t>
+  </si>
+  <si>
+    <t>Education &amp; Resources | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/education-and-resources.html</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers.report.json</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:03:53.081Z</t>
+  </si>
+  <si>
+    <t>Patients &amp; Caregivers Implant and Surgery Information</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/patients-caregivers.html</t>
+  </si>
+  <si>
     <t>en/support.report.json</t>
   </si>
   <si>
@@ -46,9 +106,6 @@
     <t>en/support</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>support-page</t>
   </si>
   <si>
@@ -61,6 +118,186 @@
     <t>https://www.zimmerbiomet.com/en/support.html</t>
   </si>
   <si>
+    <t>en/value-based-care.report.json</t>
+  </si>
+  <si>
+    <t>en/value-based-care</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:05:26.769Z</t>
+  </si>
+  <si>
+    <t>Value-Based Care</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/value-based-care.html</t>
+  </si>
+  <si>
+    <t>en/about-us/company-overview.report.json</t>
+  </si>
+  <si>
+    <t>en/about-us/company-overview</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:43.409Z</t>
+  </si>
+  <si>
+    <t>Zimmer Biomet: Shaping Orthopedic Innovations</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/about-us/company-overview.html</t>
+  </si>
+  <si>
+    <t>en/about-us/contact-us.report.json</t>
+  </si>
+  <si>
+    <t>en/about-us/contact-us</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:05:08.384Z</t>
+  </si>
+  <si>
+    <t>Get in Touch: Contact Zimmer Biomet Today</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/about-us/contact-us.html</t>
+  </si>
+  <si>
+    <t>en/about-us/leadership.report.json</t>
+  </si>
+  <si>
+    <t>en/about-us/leadership</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:51.931Z</t>
+  </si>
+  <si>
+    <t>Meet Our Leaders: Zimmer Biomet Leadership</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/about-us/leadership.html</t>
+  </si>
+  <si>
+    <t>en/about-us/our-impact.report.json</t>
+  </si>
+  <si>
+    <t>en/about-us/our-impact</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:59.456Z</t>
+  </si>
+  <si>
+    <t>Zimmer Biomet Impact: Advancing Orthopedic Care</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/about-us/our-impact.html</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/hip-replacement-products-technologies.report.json</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/hip-replacement-products-technologies</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:09.257Z</t>
+  </si>
+  <si>
+    <t>Hip Implants &amp; Replacement Technology Patient Information</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/patients-caregivers/hip-replacement-products-technologies.html</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/knee-replacement-implants-technologies.report.json</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/knee-replacement-implants-technologies</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:01.313Z</t>
+  </si>
+  <si>
+    <t>Knee Implants &amp; Replacement Technology Patient Information</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/patients-caregivers/knee-replacement-implants-technologies.html</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/mymobility-patient-care-app.report.json</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/mymobility-patient-care-app</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:36.230Z</t>
+  </si>
+  <si>
+    <t>mymobility® Patient Care Management App Information</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/patients-caregivers/mymobility-patient-care-app.html</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/robotic-surgery.report.json</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/robotic-surgery</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:27.285Z</t>
+  </si>
+  <si>
+    <t>Zimmer Biomet Robotic Surgery Patient Information</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/patients-caregivers/robotic-surgery.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/asc-solutions.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/asc-solutions</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:06:04.249Z</t>
+  </si>
+  <si>
+    <t>ZBX™ ASC Solutions- a strategic, comprehensive ASC program | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/asc-solutions.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/zb-edge.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/zb-edge</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:05:37.212Z</t>
+  </si>
+  <si>
+    <t>ZBEdge® | Dynamic Intelligence™ | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/zb-edge.html</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/knee-replacement-implants-technologies/persona-iq-smart-knee.report.json</t>
+  </si>
+  <si>
+    <t>en/patients-caregivers/knee-replacement-implants-technologies/persona-iq-smart-knee</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:04:18.255Z</t>
+  </si>
+  <si>
+    <t>Persona IQ® from Zimmer Biomet | Patient Information</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/patients-caregivers/knee-replacement-implants-technologies/Persona-IQ-smart-knee.html</t>
+  </si>
+  <si>
     <t>en/products-and-solutions/specialties/biologics.report.json</t>
   </si>
   <si>
@@ -73,7 +310,7 @@
     <t>specialty-landing-page</t>
   </si>
   <si>
-    <t>2026-04-24T17:13:05.302Z</t>
+    <t>2026-05-03T19:57:30.402Z</t>
   </si>
   <si>
     <t>Advanced Biologics Solutions | Zimmer Biomet</t>
@@ -82,6 +319,141 @@
     <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/biologics.html</t>
   </si>
   <si>
+    <t>en/products-and-solutions/specialties/cement.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/cement</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:57:38.354Z</t>
+  </si>
+  <si>
+    <t>Bone Cement Solutions for Arthroplasty | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/cement.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/cmf.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/cmf</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:57:46.155Z</t>
+  </si>
+  <si>
+    <t>Craniomaxillofacial (CMF) Solutions for Surgeons | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/cmf.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/diagnostics.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/diagnostics</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:18.828Z</t>
+  </si>
+  <si>
+    <t>Synovasure® Diagnostics for Joint Pain | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/diagnostics.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/elbow.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/elbow</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:34.466Z</t>
+  </si>
+  <si>
+    <t>Elbow Replacement Products | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/elbow.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/foot-and-ankle.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/foot-and-ankle</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:57:22.747Z</t>
+  </si>
+  <si>
+    <t>Foot &amp; Ankle Solutions | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/foot-and-ankle.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:56:40.865Z</t>
+  </si>
+  <si>
+    <t>Hip Arthroplasty Products for Surgeons from Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/hip.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/infection-solutions.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/infection-solutions</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:57:54.104Z</t>
+  </si>
+  <si>
+    <t>Infection Solutions | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/infection-solutions.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:56:49.498Z</t>
+  </si>
+  <si>
+    <t>Knee Replacement Products | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/knee.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/limb-salvage.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/limb-salvage</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:00.814Z</t>
+  </si>
+  <si>
+    <t>Limb Salvage Products from Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/limb-salvage.html</t>
+  </si>
+  <si>
     <t>en/products-and-solutions/specialties/orthogrid.report.json</t>
   </si>
   <si>
@@ -91,7 +463,7 @@
     <t>en/products-and-solutions/specialties/orthogrid</t>
   </si>
   <si>
-    <t>2026-04-24T16:59:30.082Z</t>
+    <t>2026-05-03T19:56:31.600Z</t>
   </si>
   <si>
     <t>OrthoGrid | Zimmer Biomet</t>
@@ -100,22 +472,340 @@
     <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/orthogrid.html</t>
   </si>
   <si>
+    <t>en/products-and-solutions/specialties/patient-matched-implants.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/patient-matched-implants</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:42.259Z</t>
+  </si>
+  <si>
+    <t>Patient-Matched Implants | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/patient-matched-implants.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/shoulder.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/shoulder</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:56:57.852Z</t>
+  </si>
+  <si>
+    <t>Shoulder Replacement Products | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/shoulder.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/sports-medicine.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/sports-medicine</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:57:08.139Z</t>
+  </si>
+  <si>
+    <t>Sports Medicine Products from Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/sports-medicine.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/surgical.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/surgical</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:09.954Z</t>
+  </si>
+  <si>
+    <t>Surgical Solutions from Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/surgical.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/thoracic.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/thoracic</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:26.530Z</t>
+  </si>
+  <si>
+    <t>Thoracic Products | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/thoracic.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/trauma.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/trauma</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:57:15.446Z</t>
+  </si>
+  <si>
+    <t>Trauma Products | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/trauma.html</t>
+  </si>
+  <si>
     <t>en/products-and-solutions/zb-edge/mymobility.report.json</t>
   </si>
   <si>
     <t>en/products-and-solutions/zb-edge/mymobility</t>
   </si>
   <si>
+    <t>2026-05-03T16:05:55.988Z</t>
+  </si>
+  <si>
+    <t>mymobility | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/zb-edge/mymobility.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/zb-edge/robotics.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/zb-edge/robotics</t>
+  </si>
+  <si>
+    <t>2026-05-03T16:05:44.221Z</t>
+  </si>
+  <si>
+    <t>Robotics | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/zb-edge/robotics.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/g7-acetabular-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/g7-acetabular-system</t>
+  </si>
+  <si>
     <t>product-detail-page</t>
   </si>
   <si>
-    <t>2026-04-24T19:59:07.272Z</t>
-  </si>
-  <si>
-    <t>mymobility | Zimmer Biomet</t>
-  </si>
-  <si>
-    <t>https://www.zimmerbiomet.com/en/products-and-solutions/zb-edge/mymobility.html</t>
+    <t>2026-05-03T19:59:09.775Z</t>
+  </si>
+  <si>
+    <t>G7® Acetabular System - Zimmer Biomet | Primary and Revision Hip Arthroplasty</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/hip/g7-acetabular-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/hammr-automated-hip-impaction-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/hammr-automated-hip-impaction-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:58:51.658Z</t>
+  </si>
+  <si>
+    <t>HAMMR® Automated Hip Surgical Impactor System | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/hip/hammr-automated-hip-impaction-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/taperloc-complete-hip-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/taperloc-complete-hip-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:59:19.082Z</t>
+  </si>
+  <si>
+    <t>Taperloc® Complete Hip System | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/hip/taperloc-complete-hip-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/z1-femoral-hip-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/hip/z1-femoral-hip-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:59:02.325Z</t>
+  </si>
+  <si>
+    <t>Total Hip Arthroplasty Z1 Triple Taper Hip Stem | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/hip/z1-femoral-hip-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/oxford-cementless.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/oxford-cementless</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:59:57.386Z</t>
+  </si>
+  <si>
+    <t>Oxford® Cementless Partial Knee Replacement | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/knee/oxford-cementless.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/persona-iq.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/persona-iq</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:59:29.492Z</t>
+  </si>
+  <si>
+    <t>Persona IQ® – Zimmer Biomet | Remote Patient Monitoring</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/knee/persona-iq.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/persona-knee-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/persona-knee-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:59:48.407Z</t>
+  </si>
+  <si>
+    <t>Persona® The Personalized Knee® – Zimmer Biomet | Primary Total Knee Arthroplasty</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/knee/persona-knee-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/rosa-knee-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/knee/rosa-knee-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:59:40.265Z</t>
+  </si>
+  <si>
+    <t>ROSA® Knee System | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/knee/rosa--knee-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/shoulder/comprehensive-reverse-shoulder-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/shoulder/comprehensive-reverse-shoulder-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:00:12.836Z</t>
+  </si>
+  <si>
+    <t>Comprehensive Reverse Shoulder Arthroplasty System - Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/shoulder/comprehensive-reverse-shoulder-system.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/shoulder/sidus-stem-free-shoulder.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/shoulder/sidus-stem-free-shoulder</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:00:04.934Z</t>
+  </si>
+  <si>
+    <t>Sidus® Stem-Free Cementless Total Shoulder System - Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/shoulder/sidus-stem-free-shoulder.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/sports-medicine/juggerknotless-all-suture-anchors.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/sports-medicine/juggerknotless-all-suture-anchors</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:00:29.292Z</t>
+  </si>
+  <si>
+    <t>JuggerKnotless® All-Suture Anchors - Zimmer Biomet | Soft Tissue Fixation</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/sports-medicine/juggerknotless-all-suture-anchors.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/sports-medicine/tapestry.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/sports-medicine/tapestry</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:00:20.332Z</t>
+  </si>
+  <si>
+    <t>Page Not Found</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/sports-medicine/tapestry.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/trauma/affixus-hip-fracture-nail.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/trauma/affixus-hip-fracture-nail</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:00:48.257Z</t>
+  </si>
+  <si>
+    <t>AFFIXUS® Hip Fracture Nail System</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/trauma/affixus-hip-fracture-nail.html</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/trauma/alps-mvx-mini-fragment-system.report.json</t>
+  </si>
+  <si>
+    <t>en/products-and-solutions/specialties/trauma/alps-mvx-mini-fragment-system</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:00:38.511Z</t>
+  </si>
+  <si>
+    <t>A.L.P.S. mvX™ Mini Fragment System | Zimmer Biomet</t>
+  </si>
+  <si>
+    <t>https://www.zimmerbiomet.com/en/products-and-solutions/specialties/trauma/alps-mvx-mini-fragment-system.html</t>
   </si>
 </sst>
 </file>
@@ -504,15 +1194,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="49" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -598,10 +1286,10 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -610,21 +1298,21 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
@@ -643,6 +1331,1176 @@
       </c>
       <c r="H5" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" t="s">
+        <v>165</v>
+      </c>
+      <c r="G31" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" t="s">
+        <v>181</v>
+      </c>
+      <c r="H34" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>183</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>185</v>
+      </c>
+      <c r="G35" t="s">
+        <v>186</v>
+      </c>
+      <c r="H35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H36" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>195</v>
+      </c>
+      <c r="F37" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>195</v>
+      </c>
+      <c r="F38" t="s">
+        <v>201</v>
+      </c>
+      <c r="G38" t="s">
+        <v>202</v>
+      </c>
+      <c r="H38" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>195</v>
+      </c>
+      <c r="F40" t="s">
+        <v>211</v>
+      </c>
+      <c r="G40" t="s">
+        <v>212</v>
+      </c>
+      <c r="H40" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>195</v>
+      </c>
+      <c r="F41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G41" t="s">
+        <v>217</v>
+      </c>
+      <c r="H41" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s">
+        <v>220</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>195</v>
+      </c>
+      <c r="F42" t="s">
+        <v>221</v>
+      </c>
+      <c r="G42" t="s">
+        <v>222</v>
+      </c>
+      <c r="H42" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>224</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" t="s">
+        <v>226</v>
+      </c>
+      <c r="G43" t="s">
+        <v>227</v>
+      </c>
+      <c r="H43" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" t="s">
+        <v>231</v>
+      </c>
+      <c r="G44" t="s">
+        <v>232</v>
+      </c>
+      <c r="H44" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>234</v>
+      </c>
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>195</v>
+      </c>
+      <c r="F45" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" t="s">
+        <v>237</v>
+      </c>
+      <c r="H45" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>239</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" t="s">
+        <v>241</v>
+      </c>
+      <c r="G46" t="s">
+        <v>242</v>
+      </c>
+      <c r="H46" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>195</v>
+      </c>
+      <c r="F47" t="s">
+        <v>246</v>
+      </c>
+      <c r="G47" t="s">
+        <v>247</v>
+      </c>
+      <c r="H47" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>249</v>
+      </c>
+      <c r="B48" t="s">
+        <v>250</v>
+      </c>
+      <c r="C48" t="s">
+        <v>251</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>195</v>
+      </c>
+      <c r="F48" t="s">
+        <v>252</v>
+      </c>
+      <c r="G48" t="s">
+        <v>253</v>
+      </c>
+      <c r="H48" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>255</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" t="s">
+        <v>256</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>195</v>
+      </c>
+      <c r="F49" t="s">
+        <v>257</v>
+      </c>
+      <c r="G49" t="s">
+        <v>258</v>
+      </c>
+      <c r="H49" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>260</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>261</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" t="s">
+        <v>262</v>
+      </c>
+      <c r="G50" t="s">
+        <v>263</v>
+      </c>
+      <c r="H50" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>
